--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_onoff/param_sensitivity_p99_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_onoff/param_sensitivity_p99_1Mbps.xlsx
@@ -660,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>17181.3</v>
+        <v>20871.6</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>17268.4</v>
+        <v>20986.2</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>13890.3</v>
+        <v>17090.3</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>19967.8</v>
+        <v>23776.7</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.594</v>
+        <v>0.584</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>16108.8</v>
+        <v>20003.2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18037.1</v>
+        <v>21640.4</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-0.217</v>
+        <v>-0.154</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -747,13 +747,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>19016.8</v>
+        <v>22329.2</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>19044.6</v>
+        <v>22400.4</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.018</v>
+        <v>-0.041</v>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18548.8</v>
+        <v>21673.3</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>19425.8</v>
+        <v>22765.4</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.232</v>
+        <v>0.201</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>mildly: smaller param → larger delay</t>
+          <t>mildly: larger param → larger delay</t>
         </is>
       </c>
     </row>
@@ -805,17 +805,17 @@
         <v>1</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>18855</v>
+        <v>22318.1</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>19175.6</v>
+        <v>22415.6</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.174</v>
+        <v>0.046</v>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>mildly: larger param → larger delay</t>
+          <t>no clear trend (≈flat)</t>
         </is>
       </c>
     </row>
@@ -1105,22 +1105,22 @@
         <v>0</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>17181.3</v>
+        <v>20871.6</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>4462.5</v>
+        <v>9427.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>24192.5</v>
+        <v>29852.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>15204.4</v>
+        <v>18464.4</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>17638.6</v>
+        <v>20846.9</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>18700.8</v>
+        <v>23303.3</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>108</v>
@@ -1136,22 +1136,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="24" t="n">
-        <v>17268.4</v>
+        <v>20986.2</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>7907.5</v>
+        <v>9312.5</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>23167.5</v>
+        <v>30412.5</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>15015</v>
+        <v>18329.2</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>17719.4</v>
+        <v>20831.9</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>19070.8</v>
+        <v>23797.5</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>108</v>
@@ -1161,7 +1161,7 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.012   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 17181 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.013   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 20872 µs)</t>
         </is>
       </c>
     </row>
@@ -1216,84 +1216,84 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="29" t="n">
-        <v>14351.1</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>8782.5</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>18087.5</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>12929.2</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>15425.8</v>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>14698.3</v>
-      </c>
-      <c r="H11" s="30" t="n">
+      <c r="B11" s="13" t="n">
+        <v>17090.3</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>9312.5</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>21857.5</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>15805.8</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>17808.3</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>17656.7</v>
+      </c>
+      <c r="H11" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="31" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>◀ best (min P99)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>13890.3</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>4462.5</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>18567.5</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>11888.3</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>15681.7</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>14100.8</v>
-      </c>
-      <c r="H12" s="21" t="n">
+      <c r="B12" s="24" t="n">
+        <v>17339.4</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>10162.5</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>22807.5</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>15025.8</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>18297.5</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>18695</v>
+      </c>
+      <c r="H12" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
+      <c r="I12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B13" s="29" t="n">
-        <v>17521.4</v>
+        <v>21617.5</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>12937.5</v>
+        <v>16372.5</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>21002.5</v>
+        <v>26077.5</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>14595</v>
+        <v>17987.5</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>18059.2</v>
+        <v>21700</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>19910</v>
+        <v>25165</v>
       </c>
       <c r="H13" s="30" t="n">
         <v>36</v>
@@ -1305,22 +1305,22 @@
         <v>3</v>
       </c>
       <c r="B14" s="24" t="n">
-        <v>18736.7</v>
+        <v>22511.4</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>15492.5</v>
+        <v>17357.5</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>24192.5</v>
+        <v>29812.5</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>16096.7</v>
+        <v>19349.2</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>18278.3</v>
+        <v>21306.7</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>21835</v>
+        <v>26878.3</v>
       </c>
       <c r="H14" s="25" t="n">
         <v>36</v>
@@ -1332,22 +1332,22 @@
         <v>4</v>
       </c>
       <c r="B15" s="29" t="n">
-        <v>18881.9</v>
+        <v>23238.1</v>
       </c>
       <c r="C15" s="29" t="n">
-        <v>16352.5</v>
+        <v>18462.5</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>23472.5</v>
+        <v>30412.5</v>
       </c>
       <c r="E15" s="29" t="n">
-        <v>17089.2</v>
+        <v>20675.8</v>
       </c>
       <c r="F15" s="29" t="n">
-        <v>18387.5</v>
+        <v>22190</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>21169.2</v>
+        <v>26848.3</v>
       </c>
       <c r="H15" s="30" t="n">
         <v>36</v>
@@ -1359,22 +1359,22 @@
         <v>5</v>
       </c>
       <c r="B16" s="24" t="n">
-        <v>19967.8</v>
+        <v>23776.7</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>16477.5</v>
+        <v>18672.5</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>23552.5</v>
+        <v>28647.5</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>18060</v>
+        <v>21536.7</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>20241.7</v>
+        <v>23734.2</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>21601.7</v>
+        <v>26059.2</v>
       </c>
       <c r="H16" s="25" t="n">
         <v>36</v>
@@ -1384,7 +1384,7 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.594   |   strongly: larger param → larger delay   |   recommended QSRC = 1 (lowest mean P99 = 13890 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.584   |   strongly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 17090 µs)</t>
         </is>
       </c>
     </row>
@@ -1443,22 +1443,22 @@
         <v>1</v>
       </c>
       <c r="B21" s="29" t="n">
-        <v>18037.1</v>
+        <v>21640.4</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>15452.5</v>
+        <v>18242.5</v>
       </c>
       <c r="D21" s="29" t="n">
-        <v>21002.5</v>
+        <v>24582.5</v>
       </c>
       <c r="E21" s="29" t="n">
-        <v>16567.5</v>
+        <v>20115.8</v>
       </c>
       <c r="F21" s="29" t="n">
-        <v>18227.5</v>
+        <v>21563.3</v>
       </c>
       <c r="G21" s="29" t="n">
-        <v>19316.2</v>
+        <v>23242.1</v>
       </c>
       <c r="H21" s="30" t="n">
         <v>72</v>
@@ -1470,22 +1470,22 @@
         <v>2</v>
       </c>
       <c r="B22" s="24" t="n">
-        <v>17528.8</v>
+        <v>21143.1</v>
       </c>
       <c r="C22" s="24" t="n">
-        <v>11057.5</v>
+        <v>14322.5</v>
       </c>
       <c r="D22" s="24" t="n">
-        <v>22577.5</v>
+        <v>27127.5</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>15058.3</v>
+        <v>18272.9</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>17854.6</v>
+        <v>20966.2</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>19673.3</v>
+        <v>24190</v>
       </c>
       <c r="H22" s="25" t="n">
         <v>72</v>
@@ -1497,22 +1497,22 @@
         <v>3</v>
       </c>
       <c r="B23" s="13" t="n">
-        <v>16108.8</v>
+        <v>20003.2</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>4462.5</v>
+        <v>9312.5</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>24192.5</v>
+        <v>30412.5</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>13703.3</v>
+        <v>16801.7</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>16955</v>
+        <v>19988.8</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>17667.9</v>
+        <v>23219.2</v>
       </c>
       <c r="H23" s="21" t="n">
         <v>72</v>
@@ -1526,7 +1526,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.217   |   mildly: smaller param → larger delay   |   recommended PSRC = 3 (lowest mean P99 = 16109 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.154   |   mildly: smaller param → larger delay   |   recommended PSRC = 3 (lowest mean P99 = 20003 µs)</t>
         </is>
       </c>
     </row>
@@ -1626,19 +1626,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="29" t="n">
-        <v>19044.6</v>
+        <v>22400.4</v>
       </c>
       <c r="C5" s="29" t="n">
-        <v>17577.5</v>
+        <v>21077.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>20437.5</v>
+        <v>24497.5</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>18636.9</v>
+        <v>21951.1</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>19452.2</v>
+        <v>22849.7</v>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
@@ -1655,19 +1655,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>19016.8</v>
+        <v>22329.2</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>17572.5</v>
+        <v>20157.5</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>20682.5</v>
+        <v>24122.5</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>18464.2</v>
+        <v>21846.4</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>19569.4</v>
+        <v>22811.9</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.018   |   no clear trend (≈flat)   |   recommended CWds = 1 (lowest mean P99 = 19017 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.041   |   no clear trend (≈flat)   |   recommended CWds = 1 (lowest mean P99 = 22329 µs)</t>
         </is>
       </c>
     </row>
@@ -1741,52 +1741,56 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="29" t="n">
-        <v>18972.9</v>
-      </c>
-      <c r="C11" s="29" t="n">
-        <v>18567.5</v>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>19252.5</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>18829.2</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>19116.7</v>
-      </c>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="B11" s="13" t="n">
+        <v>21673.3</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>20887.5</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>22412.5</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>21600</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>21746.7</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="I11" s="31" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>◀ best (min P99)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="B12" s="24" t="n">
-        <v>19425.8</v>
+        <v>22374.6</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>18277.5</v>
+        <v>21642.5</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>20682.5</v>
+        <v>22932.5</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>18934.2</v>
+        <v>22141.7</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>19917.5</v>
+        <v>22607.5</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -1803,19 +1807,19 @@
         <v>2</v>
       </c>
       <c r="B13" s="29" t="n">
-        <v>19372.5</v>
+        <v>22765.4</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>18202.5</v>
+        <v>21637.5</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>20437.5</v>
+        <v>24217.5</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>18676.7</v>
+        <v>22150</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>20068.3</v>
+        <v>23380.8</v>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
@@ -1832,19 +1836,19 @@
         <v>3</v>
       </c>
       <c r="B14" s="24" t="n">
-        <v>19008.8</v>
+        <v>22485</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>18217.5</v>
+        <v>20682.5</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>19967.5</v>
+        <v>23527.5</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>18475.8</v>
+        <v>21900</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>19541.7</v>
+        <v>23070</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -1857,56 +1861,52 @@
       <c r="I14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>18548.8</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>17577.5</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>20267.5</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>18024.2</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>19073.3</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="B15" s="29" t="n">
+        <v>22565.8</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>21147.5</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>23392.5</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>22190.8</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>22940.8</v>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
+      <c r="I15" s="31" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n">
         <v>5</v>
       </c>
       <c r="B16" s="24" t="n">
-        <v>18855.4</v>
+        <v>22324.6</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>17572.5</v>
+        <v>20157.5</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>20127.5</v>
+        <v>24497.5</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>18363.3</v>
+        <v>21410</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>19347.5</v>
+        <v>23239.2</v>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.232   |   mildly: smaller param → larger delay   |   recommended QSRC = 4 (lowest mean P99 = 18549 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.201   |   mildly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 21673 µs)</t>
         </is>
       </c>
     </row>
@@ -1980,19 +1980,19 @@
         <v>1</v>
       </c>
       <c r="B21" s="13" t="n">
-        <v>18855</v>
+        <v>22318.1</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>17572.5</v>
+        <v>20157.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>20337.5</v>
+        <v>23992.5</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>18516.2</v>
+        <v>21862.9</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>19193.8</v>
+        <v>22773.3</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -2013,19 +2013,19 @@
         <v>2</v>
       </c>
       <c r="B22" s="24" t="n">
-        <v>19061.5</v>
+        <v>22360.6</v>
       </c>
       <c r="C22" s="24" t="n">
-        <v>17782.5</v>
+        <v>21147.5</v>
       </c>
       <c r="D22" s="24" t="n">
-        <v>20682.5</v>
+        <v>24497.5</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>18420</v>
+        <v>21848.8</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>19702.9</v>
+        <v>22872.5</v>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
@@ -2042,19 +2042,19 @@
         <v>3</v>
       </c>
       <c r="B23" s="29" t="n">
-        <v>19175.6</v>
+        <v>22415.6</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>18112.5</v>
+        <v>20682.5</v>
       </c>
       <c r="D23" s="29" t="n">
-        <v>20437.5</v>
+        <v>24217.5</v>
       </c>
       <c r="E23" s="29" t="n">
-        <v>18715.4</v>
+        <v>21984.6</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>19635.8</v>
+        <v>22846.7</v>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.174   |   mildly: larger param → larger delay   |   recommended PSRC = 1 (lowest mean P99 = 18855 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.046   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 22318 µs)</t>
         </is>
       </c>
     </row>
